--- a/doc/需求规格说明书.xlsx
+++ b/doc/需求规格说明书.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" tabRatio="500"/>
+    <workbookView windowWidth="12800" windowHeight="12080" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="需求规格说明书" sheetId="1" r:id="rId1"/>
     <sheet name="编号规则说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">需求规格说明书!$A$4:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">需求规格说明书!$A$4:$I$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -372,18 +372,13 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
       <t>username</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
       </rPr>
       <t>已存在；</t>
     </r>
@@ -398,8 +393,8 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
+        <rFont val="宋体"/>
+        <charset val="1"/>
       </rPr>
       <t>与注册时一致</t>
     </r>
@@ -415,25 +410,28 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">同 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
+      <t>同</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">F-02-01 </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
+        <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
       <t>成功场景</t>
@@ -441,18 +439,29 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>首页显示“欢迎，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
+      <t>首页显示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>欢迎，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
       </rPr>
       <t>{username}”</t>
     </r>
@@ -939,6 +948,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve"> </t>
     </r>
     <r>
@@ -1270,7 +1285,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1502,10 +1517,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF1F4E79"/>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
       <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1516,9 +1536,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF666666"/>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F4E79"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -2068,6 +2088,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2107,63 +2133,57 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常規" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="貨幣" xfId="2" builtinId="4"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
     <cellStyle name="百分比" xfId="3" builtinId="5"/>
     <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="貨幣[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超鏈接" xfId="6" builtinId="8"/>
-    <cellStyle name="已訪問的超鏈接" xfId="7" builtinId="9"/>
-    <cellStyle name="註釋" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文字" xfId="9" builtinId="11"/>
-    <cellStyle name="標題" xfId="10" builtinId="15"/>
-    <cellStyle name="解釋性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="標題 1" xfId="12" builtinId="16"/>
-    <cellStyle name="標題 2" xfId="13" builtinId="17"/>
-    <cellStyle name="標題 3" xfId="14" builtinId="18"/>
-    <cellStyle name="標題 4" xfId="15" builtinId="19"/>
-    <cellStyle name="輸入" xfId="16" builtinId="20"/>
-    <cellStyle name="輸出" xfId="17" builtinId="21"/>
-    <cellStyle name="計算" xfId="18" builtinId="22"/>
-    <cellStyle name="檢查儲存格" xfId="19" builtinId="23"/>
-    <cellStyle name="鏈接儲存格" xfId="20" builtinId="24"/>
-    <cellStyle name="匯總" xfId="21" builtinId="25"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
     <cellStyle name="好" xfId="22" builtinId="26"/>
     <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="適中" xfId="24" builtinId="28"/>
-    <cellStyle name="強調文字顏色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 強調文字顏色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 強調文字顏色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 強調文字顏色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="強調文字顏色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 強調文字顏色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 強調文字顏色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 強調文字顏色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="強調文字顏色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 強調文字顏色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 強調文字顏色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 強調文字顏色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="強調文字顏色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 強調文字顏色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 強調文字顏色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 強調文字顏色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="強調文字顏色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 強調文字顏色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 強調文字顏色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 強調文字顏色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="強調文字顏色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 強調文字顏色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 強調文字顏色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 強調文字顏色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -2760,16 +2780,16 @@
       <c r="B7" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="18" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="18" t="s">
         <v>28</v>
       </c>
       <c r="G7" s="13" t="s">
@@ -2788,13 +2808,13 @@
       <c r="C8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="18" t="s">
         <v>32</v>
       </c>
       <c r="G8" s="13" t="s">
@@ -2854,31 +2874,31 @@
       <c r="I10" s="16"/>
     </row>
     <row r="11" ht="33.75" customHeight="1" spans="1:9">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="21"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" ht="33.75" customHeight="1" spans="1:9">
       <c r="A12" s="12" t="s">
@@ -3037,34 +3057,34 @@
       <c r="I17" s="16"/>
     </row>
     <row r="18" ht="29" spans="1:9">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="31" t="s">
         <v>84</v>
       </c>
       <c r="H18" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="I18" s="31"/>
+      <c r="I18" s="26"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:I17" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:I18" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="2">
